--- a/research/traditional_assets/database/data/lithuania/lithuania_software_system_application.xlsx
+++ b/research/traditional_assets/database/data/lithuania/lithuania_software_system_application.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.1804347826086957</v>
+        <v>-0.3781512605042017</v>
       </c>
       <c r="H2">
-        <v>-0.1804347826086957</v>
+        <v>-0.3781512605042017</v>
       </c>
       <c r="I2">
-        <v>-0.1239130434782609</v>
+        <v>-1.974789915966386</v>
       </c>
       <c r="J2">
-        <v>-0.1239130434782609</v>
+        <v>-1.974789915966386</v>
       </c>
       <c r="K2">
-        <v>-0.171</v>
+        <v>-0.47</v>
       </c>
       <c r="L2">
-        <v>-0.1239130434782609</v>
+        <v>-1.974789915966386</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,55 +627,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.008999999999999999</v>
+        <v>0.004</v>
       </c>
       <c r="V2">
-        <v>0.0003422053231939163</v>
+        <v>8.000000000000001e-05</v>
       </c>
       <c r="W2">
-        <v>-2.342465753424658</v>
+        <v>6.714285714285714</v>
       </c>
       <c r="X2">
-        <v>0.07423362824545246</v>
+        <v>0.1369730675790308</v>
       </c>
       <c r="Y2">
-        <v>-2.416699381670111</v>
+        <v>6.577312646706683</v>
       </c>
       <c r="Z2">
-        <v>2.546125461254613</v>
+        <v>0.505307855626327</v>
       </c>
       <c r="AA2">
-        <v>-0.3154981549815499</v>
+        <v>-0.9978768577494691</v>
       </c>
       <c r="AB2">
-        <v>0.07338468353752776</v>
+        <v>0.1361605820636923</v>
       </c>
       <c r="AC2">
-        <v>-0.3888828385190776</v>
+        <v>-1.134037439813161</v>
       </c>
       <c r="AD2">
-        <v>0.546</v>
+        <v>0.525</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.546</v>
+        <v>0.525</v>
       </c>
       <c r="AG2">
-        <v>0.537</v>
+        <v>0.521</v>
       </c>
       <c r="AH2">
-        <v>0.02033822543395664</v>
+        <v>0.01039089559623949</v>
       </c>
       <c r="AI2">
-        <v>1.1375</v>
+        <v>4.999999999999998</v>
       </c>
       <c r="AJ2">
-        <v>0.0200096881171517</v>
+        <v>0.01031254329882623</v>
       </c>
       <c r="AK2">
-        <v>1.140127388535032</v>
+        <v>5.158415841584157</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -684,10 +684,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>-4.706896551724138</v>
+        <v>-1.177130044843049</v>
       </c>
       <c r="AP2">
-        <v>-4.629310344827586</v>
+        <v>-1.168161434977578</v>
       </c>
     </row>
     <row r="3">
@@ -707,22 +707,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.1804347826086957</v>
+        <v>-0.3781512605042017</v>
       </c>
       <c r="H3">
-        <v>-0.1804347826086957</v>
+        <v>-0.3781512605042017</v>
       </c>
       <c r="I3">
-        <v>-0.1239130434782609</v>
+        <v>-1.974789915966386</v>
       </c>
       <c r="J3">
-        <v>-0.1239130434782609</v>
+        <v>-1.974789915966386</v>
       </c>
       <c r="K3">
-        <v>-0.171</v>
+        <v>-0.47</v>
       </c>
       <c r="L3">
-        <v>-0.1239130434782609</v>
+        <v>-1.974789915966386</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -746,55 +746,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.008999999999999999</v>
+        <v>0.004</v>
       </c>
       <c r="V3">
-        <v>0.0003422053231939163</v>
+        <v>8.000000000000001e-05</v>
       </c>
       <c r="W3">
-        <v>-2.342465753424658</v>
+        <v>6.714285714285714</v>
       </c>
       <c r="X3">
-        <v>0.07423362824545246</v>
+        <v>0.1369730675790308</v>
       </c>
       <c r="Y3">
-        <v>-2.416699381670111</v>
+        <v>6.577312646706683</v>
       </c>
       <c r="Z3">
-        <v>2.546125461254613</v>
+        <v>0.505307855626327</v>
       </c>
       <c r="AA3">
-        <v>-0.3154981549815499</v>
+        <v>-0.9978768577494691</v>
       </c>
       <c r="AB3">
-        <v>0.07338468353752776</v>
+        <v>0.1361605820636923</v>
       </c>
       <c r="AC3">
-        <v>-0.3888828385190776</v>
+        <v>-1.134037439813161</v>
       </c>
       <c r="AD3">
-        <v>0.546</v>
+        <v>0.525</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.546</v>
+        <v>0.525</v>
       </c>
       <c r="AG3">
-        <v>0.537</v>
+        <v>0.521</v>
       </c>
       <c r="AH3">
-        <v>0.02033822543395664</v>
+        <v>0.01039089559623949</v>
       </c>
       <c r="AI3">
-        <v>1.1375</v>
+        <v>4.999999999999998</v>
       </c>
       <c r="AJ3">
-        <v>0.0200096881171517</v>
+        <v>0.01031254329882623</v>
       </c>
       <c r="AK3">
-        <v>1.140127388535032</v>
+        <v>5.158415841584157</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -803,10 +803,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>-4.706896551724138</v>
+        <v>-1.177130044843049</v>
       </c>
       <c r="AP3">
-        <v>-4.629310344827586</v>
+        <v>-1.168161434977578</v>
       </c>
     </row>
   </sheetData>
